--- a/volatility/history/2026-09-28/mootdx_波动率数据汇总_20260928.xlsx
+++ b/volatility/history/2026-09-28/mootdx_波动率数据汇总_20260928.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$G$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -914,8 +914,62 @@
         <v>15.73</v>
       </c>
     </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>300999.SZ</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>金龙鱼</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>600418.SH</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>17.71</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>